--- a/ig/nr-update-relationship/StructureDefinition-fr-core-practitioner-role-profession.xlsx
+++ b/ig/nr-update-relationship/StructureDefinition-fr-core-practitioner-role-profession.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-18T12:45:56+00:00</t>
+    <t>2024-03-22T10:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
